--- a/data/employees/EMP058/AST-EMP058-06.xlsx
+++ b/data/employees/EMP058/AST-EMP058-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,215 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Skills Matrix - Jamie Brown (HR)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jamie Brown | Role: Manager | Location: Austin | Date: 2025-03-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>86</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Skills</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Last Review Date</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Rating</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMP006</t>
+          <t>EMP058</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp058 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Azure AI, Fabric</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>71</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4.2</v>
+          <t>Section 1: Department KPI performance. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMP011</t>
+          <t>EMP058</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp058 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Synapse, TypeScript</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3.9</v>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMP016</t>
+          <t>EMP058</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp058 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Python, SQL</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>93</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMP021</t>
+          <t>EMP058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp058 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>63</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>69</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>97</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>99</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>78</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>69</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>68</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>88</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>76</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>72</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>66</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>94</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>98</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>95</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>73</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>83</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>96</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp058 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>75</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ontology, MLOps</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP058</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP058 contributes to ast emp058 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>